--- a/tests/browser/fixtures/pdc/presupuesto-mini.xlsx
+++ b/tests/browser/fixtures/pdc/presupuesto-mini.xlsx
@@ -95,13 +95,13 @@
     <t>APU-001</t>
   </si>
   <si>
-    <t>TEJA DE ZINC</t>
+    <t>ZZTEST TEJA DE ZINC</t>
   </si>
   <si>
     <t>MAT-CUBIERTAS</t>
   </si>
   <si>
-    <t>AYUDANTE</t>
+    <t>ZZTEST AYUDANTE</t>
   </si>
   <si>
     <t>HC</t>
@@ -140,13 +140,13 @@
     <t>APU-002</t>
   </si>
   <si>
-    <t>CONCRETO 4000PSI</t>
+    <t>ZZTEST CONCRETO 4000PSI</t>
   </si>
   <si>
     <t>MAT-CONCRETOS</t>
   </si>
   <si>
-    <t>SERVICIO BOMBEO</t>
+    <t>ZZTEST SERVICIO BOMBEO</t>
   </si>
   <si>
     <t>EQUIPOS</t>
